--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/phi-4/aae/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/phi-4/aae/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D2">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D3">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="E3">
         <v>4</v>
       </c>
       <c r="G3">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H3">
         <v>426</v>
